--- a/artfynd/A 20781-2024 artfynd.xlsx
+++ b/artfynd/A 20781-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117863639</v>
+        <v>117864235</v>
       </c>
       <c r="B2" t="n">
-        <v>56718</v>
+        <v>104830</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100091</v>
+        <v>221137</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sjöbrännan, Norr-Greningen, Lit, Jmt</t>
@@ -789,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117864235</v>
+        <v>117863639</v>
       </c>
       <c r="B3" t="n">
-        <v>104828</v>
+        <v>56719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,28 +789,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221137</v>
+        <v>100091</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöbrännan, Norr-Greningen, Lit, Jmt</t>

--- a/artfynd/A 20781-2024 artfynd.xlsx
+++ b/artfynd/A 20781-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>117863639</v>
       </c>
       <c r="B2" t="n">
-        <v>56721</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,12 +787,7 @@
         <v>117864235</v>
       </c>
       <c r="B3" t="n">
-        <v>104833</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20781-2024 artfynd.xlsx
+++ b/artfynd/A 20781-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117863639</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,8 +888,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117864235</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>